--- a/output/Chatbot_Scoring_Results_v5.xlsx
+++ b/output/Chatbot_Scoring_Results_v5.xlsx
@@ -34,7 +34,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,27 +48,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -98,19 +83,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -514,7 +490,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +500,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -535,7 +511,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.5%</t>
         </is>
       </c>
     </row>
@@ -546,7 +522,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -556,7 +532,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -566,7 +542,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -580,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -593,8 +569,6 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -638,7 +612,7 @@
           <t>Score (%)</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Golden Dataset Rows</t>
         </is>
@@ -646,16 +620,6 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Response Col Used</t>
         </is>
       </c>
     </row>
@@ -738,7 +702,32 @@
 • Sesame/Groundnut – line sowing
 • Recommended dose per crop
 • Atrazine @2 gm/L water (PE) for Maize
-• Line sowing with seed drills</t>
+• Line sowing with seed drills
+• Rice: Anjali
+• Purnima
+• Annada
+• Maize: Pro-4212
+• Pusa Early Makka-1
+• Vivek hybrid-9 &amp; 17
+• Moong: Pusa Vishal
+• BM-4
+• HUM-12
+• Pragya (rabi)
+• Pairi Moong (rabi)
+• Direct seeding of sprouted rice seed under puddled condition
+• 20% higher seed rate for rice
+• proper spacing + Rhizobium for pulses
+• Atrazine for Maize PE
+• Recommended dose
+• Seed supply through corporation
+• Existing varieties
+• Thinning and gap filling
+• re-sowing
+• sprouted seed if nursery unavailable
+• life-saving irrigation
+• in situ SWC
+• inter-cultural implements through RKVY
+• farm pond through IWSM</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -748,7 +737,10 @@
 • Anjali
 • Danteshwari
 • Asha [~fuzzy]
-• Recommended dose per crop [~semantic]</t>
+• Purnima
+• Annada
+• Recommended dose per crop [~semantic]
+• sprouted seed if nursery unavailable [~semantic]</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -792,30 +784,42 @@
 • Atrazine @2 gm/L water PE
 • Sesame/Groundnut – line sowing
 • Atrazine @2 gm/L water (PE) for Maize
-• Line sowing with seed drills</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>13</v>
+• Line sowing with seed drills
+• Rice: Anjali
+• Maize: Pro-4212
+• Pusa Early Makka-1
+• Vivek hybrid-9 &amp; 17
+• Moong: Pusa Vishal
+• BM-4
+• HUM-12
+• Pragya (rabi)
+• Pairi Moong (rabi)
+• Direct seeding of sprouted rice seed under puddled condition
+• 20% higher seed rate for rice
+• proper spacing + Rhizobium for pulses
+• Atrazine for Maize PE
+• Recommended dose
+• Seed supply through corporation
+• Existing varieties
+• Thinning and gap filling
+• re-sowing
+• life-saving irrigation
+• in situ SWC
+• inter-cultural implements through RKVY
+• farm pond through IWSM</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>12.7</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Surajpur · rows 2</t>
+          <t>Surajpur · rows 2, 5, 10</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Normal onset (15 Jun-15 Jul)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>English response (normal onset)</t>
         </is>
       </c>
     </row>
@@ -830,22 +834,22 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>I am treating Mal soil as high land/upland. This is a proof-of-concept forecast as of 9 June 2026.
-20% chance: onset before 24 June.  
-In this case:
-- After steady rain begins, line-sow Tulsi, Vandana, Kalinga-3 or Vanprabha paddy.
+          <t>I am treating Mal land as high land/upland and rainfed.
+65% chance: onset from 10 to 24 June.  
+In this case:
+- After steady rain wets the soil, line-sow paddy.
+- Suitable varieties: Tulsi, Vandana, Aditya, Kalinga-3 or Anjali.
 - Apply the locally recommended fertilizer dose.
-- Open conservation furrows to retain rainwater.
-60% chance: onset from 24 June to 8 July.  
-In this case:
-- Keep seed and field ready; line-sow when continuous rain starts, not after one shower.
-- Prefer upland paddy such as Indira Barani Dhan-1, Anjali or Danteshwari.
-- Use conservation furrows because you have no irrigation.
-20% chance: onset after 8 July.  
-In this case:
-- Up to 15 July, follow line sowing with early upland varieties.
-- During 16–31 July, direct-sow sprouted Anjali, Poornima, Annada or Danteshwari seed in puddled soil; increase seed rate by 20%.
-- If onset slips beyond 31 July, paddy on Mal land becomes very risky; consult the nearest KVK before sowing.</t>
+15% chance: onset before 10 June.  
+In this case:
+- Prepare the field, but do not sow after only one shower.
+- If rain remains steady into mid-June, line-sow the varieties listed above.
+- If a dry spell follows, thin crowded plants, fill gaps and make conservation furrows.
+20% chance: onset after 24 June.  
+In this case:
+- If rain starts by 15 July, line-sow upland paddy.
+- If it starts 16–31 July, direct-sow sprouted Anjali, Purnima, Annada or Danteshwari seed and raise seed rate by 20%.
+- After 31 July, upland paddy without irrigation is high-risk; consult the nearest KVK or agricultural office.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -855,61 +859,85 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>• Sawarna
-• MTU-1010
+          <t>• MTU-1010
 • PA-6444
 • PHB-71
 • KRH-1
 • Indira sona
+• Purnima
+• Indira barani dhan-1
+• Danteshwari
 • IGKV R1
+• Use 15-20 day old seedlings for transplanting
+• apply 15-20 kg ZnSO4 before planting
+• apply recommended fertilizer
+• Recommended dose + 15-20 kg ZnSO4/ha
+• ZnSO4 @15-20 kg/ha
+• ZnSO4 supply
+• Sawarna
 • Samleshwari
 • Grow short/medium-duration variety
 • direct seeding of sprouted rice seed under puddled condition
 • Recommended dose
-• Seed supply through corporation</t>
+• Seed supply through corporation
+• Early variety (short duration)
+• Grow short-duration variety
+• direct seeding of sprouted seed under puddled condition
+• weed mulching
+• biasi
+• foliar application of urea for established crops
+• Foliar urea if stress
+• Seed supply</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>• Recommended dose [~fuzzy]
-• direct seeding of sprouted rice seed under puddled condition [~semantic]</t>
+          <t>• Purnima
+• Danteshwari
+• apply recommended fertilizer [~fuzzy]
+• Recommended dose [~fuzzy]
+• direct seeding of sprouted seed under puddled condition [~semantic]</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>• Sawarna
-• MTU-1010
+          <t>• MTU-1010
 • PA-6444
 • PHB-71
 • KRH-1
 • Indira sona
+• Indira barani dhan-1
 • IGKV R1
+• Use 15-20 day old seedlings for transplanting
+• apply 15-20 kg ZnSO4 before planting
+• Recommended dose + 15-20 kg ZnSO4/ha
+• ZnSO4 @15-20 kg/ha
+• ZnSO4 supply
+• Sawarna
 • Samleshwari
 • Grow short/medium-duration variety
-• Seed supply through corporation</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>16.7</v>
+• direct seeding of sprouted rice seed under puddled condition
+• Seed supply through corporation
+• Early variety (short duration)
+• Grow short-duration variety
+• weed mulching
+• biasi
+• foliar application of urea for established crops
+• Foliar urea if stress
+• Seed supply</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Surajpur · rows 6</t>
+          <t>Surajpur · rows 3, 6, 8</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Delayed 2-4 weeks (16-31 Jul)</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>English response (2 week delay)</t>
         </is>
       </c>
     </row>
@@ -949,7 +977,29 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>• Purnima
+          <t>• Sawarna
+• Jaldubi
+• PA-6444
+• Mahamaya
+• Danteshwari
+• Bambleswari
+• Karma Mahsuri
+• Swarna sub-1
+• Standard transplanting
+• recommended package
+• Recommended dose
+• Normal
+• Sawarna sub-1
+• MTU-1010
+• PHB-71
+• KRH-1
+• Indira sona
+• IGKV R2/Durgeshwari
+• IGKV R1244/Maheshwari
+• Grow short/medium-duration variety
+• direct seeding of sprouted rice seed under puddled condition
+• Seed supply through corporation
+• Purnima
 • MTU-1010 (early + mid-early duration)
 • Short-duration variety
 • sprouted seed under puddled condition
@@ -962,909 +1012,93 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>• MTU-1010 (early + mid-early duration) [name match]
+          <t>• Mahamaya
+• Danteshwari [~fuzzy]
+• Bambleswari
+• MTU-1010
+• MTU-1010 (early + mid-early duration) [name match]
+• direct seeding of sprouted rice seed under puddled condition [~semantic]
 • sprouted seed under puddled condition [~semantic]
 • Seed supply [~semantic]</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>• Purnima
-• Short-duration variety
-• weed mulching
-• biasi
-• foliar urea for established crops
-• Foliar urea if stress</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Surajpur · rows 9</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Partial — some key advice missing</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Delayed 6-8 weeks (1-15 Aug)</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>English response (6 week delay)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>I farm on Tikra land in Surajpur block, Surajpur district, no irrigation facility. My rice, arhar, maize all look stressed and are drying up. What should I do to save the crop, and is there any pond or water-saving structure I can get?</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>I can advise only on weather-informed paddy practices. For the other stressed crops, contact the nearest KVK or local agricultural office.
-70% chance: onset from 12 to 22 June.  
-In this case:
-- Weed and use weeds as mulch; lightly intercultivate to reduce moisture loss.
-- Open conservation furrows to catch rain.
-- After moisture returns, spray 2% urea on paddy.
-15% chance: onset before 12 June.  
-In this case:
-- Repair bunds and conservation furrows now.
-- Thin overcrowded paddy and fill small gaps after rain.
-- Apply 2% urea spray once plants recover.
-15% chance: onset after 22 June.  
-In this case:
-- Paddy on Tikra land faces high drying risk; thin plants and weed-mulch immediately.
-- Prioritise any available water for one life-saving irrigation.
-- Ask the Block Agriculture/Watershed Office about farm-pond assistance under the IWSM programme; confirm current eligibility locally.
-This is a proof-of-concept recommendation.</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Surajpur / upland / No irrigation</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>• Existing varieties
-• Thinning and gap filling
-• re-sowing
-• sprouted seed if nursery unavailable
-• life-saving irrigation
-• in situ SWC
-• inter-cultural implements through RKVY
-• farm pond through IWSM</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>• life-saving irrigation</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>• Existing varieties
-• Thinning and gap filling
-• re-sowing
-• sprouted seed if nursery unavailable
-• in situ SWC
-• inter-cultural implements through RKVY
-• farm pond through IWSM</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Surajpur · rows 10</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Normal onset followed by 15-20 days dry spell</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>English response (normal onset)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>In Balrampur block, Balrampur district, my land is Mal type with no irrigation. Which dhan variety should I transplant this year and do I need to add some chemical?</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Is your “Mal” land high land, medium land, or low land? Please choose one so I can give the right paddy advice.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Balrampur / midland / No irrigation</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>• MTU-1010
+          <t>• Sawarna
+• Jaldubi
 • PA-6444
-• PHB-71
-• KRH-1
-• Indira Sona
-• Purnima
-• Indira Barani Dhan-1
-• Samleshwari
-• IGKV R1
-• 15-20 days old seedling for transplanting
-• apply 15-20 kg ZnSO4 before planting
-• recommended dose of fertilizer
-• As recommended
-• 15-20 kg ZnSO4/ha
-• Not specified</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>• MTU-1010
-• PA-6444
-• PHB-71
-• KRH-1
-• Indira Sona
-• Purnima
-• Indira Barani Dhan-1
-• Samleshwari
-• IGKV R1
-• 15-20 days old seedling for transplanting
-• apply 15-20 kg ZnSO4 before planting
-• recommended dose of fertilizer
-• As recommended
-• 15-20 kg ZnSO4/ha
-• Not specified</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Balrampur · rows 3</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Delayed 2 weeks (15 Jun-15 Jul)</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>English response (2 week delay)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Ramanujganj, Balrampur district — my field is Gabhar, no irrigation. Which dhan variety is suitable for me this year?</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Your Gabhar field is classified as low land.
-20% chance: onset before 12 June.
-In this case:
-- Use Swarna, Swarna Sub-1, or Mahamaya.
-- Start nursery only after continuous rain begins.
-- Transplant 15–20-day-old seedlings.
-60% chance: onset from 12 to 22 June.
-In this case:
-- Swarna, Swarna Sub-1, Mahamaya, or Danteshwari are suitable.
-- Repair bunds to conserve rainwater.
-- Transplant 15–20-day-old seedlings.
-20% chance: onset after 22 June.
-In this case:
-- By 15 July: use the varieties above.
-- During 16–31 July: prefer MTU-1010, PA-6444, or Indira Sona; direct-sow sprouted seed in a puddled field.
-- During 1–15 August: prefer Purnima or MTU-1010; later onset makes rainfed paddy highly risky.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Balrampur / lowland / No irrigation</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>• Swarna
-• MTU-1010
-• PA-6444
-• PHB-71
-• KRH-1
-• Indira Sona
-• Grow short and medium duration variety
-• direct seeding of sprouted rice seed under puddled condition
-• As recommended
-• Not specified</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>• Swarna
-• MTU-1010
-• PA-6444
-• Indira Sona</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>• PHB-71
-• KRH-1
-• Grow short and medium duration variety
-• direct seeding of sprouted rice seed under puddled condition
-• As recommended
-• Not specified</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Balrampur · rows 7</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Partial — some key advice missing</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Delayed 4-6 weeks (16-31 Jul)</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>English response (4 week delay)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>In Wadrafnagar, Balrampur district, I have Marhan upland, no irrigation source. What should I sow now and how?</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Your Marhan field is upland and rainfed.
-60% chance: onset from 10 June to 24 June.
-In this case:
-- After steady rain, line-sow paddy; do not sow on one shower.
-- From 15 June, use an upland variety such as Vandana, Anjali, Tulsi or Indira Barani Dhan-1.
-- Apply the locally recommended fertilizer dose.
-20% chance: onset before 10 June.
-In this case:
-- Prepare the field and moisture-conservation furrows.
-- Sow only after continuous rain starts.
-- Confirm variety timing with the nearest KVK because this early window is not covered by this PoC.
-20% chance: onset after 24 June.
-In this case:
-- By 15 July: line-sow the upland varieties listed above.
-- During 16–31 July: direct-sow sprouted Anjali, Purnima or Annda seed in puddled soil; increase seed rate by 20%.
-- After 31 July, unirrigated upland paddy is very risky; consult KVK before sowing.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Balrampur / upland / No irrigation</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>No golden dataset match — No row matches (district + land type + irrigation + scenario)</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Delayed 6-8 weeks (1-15 Aug)</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>English response (6 week delay)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>My field in Bagicha, Jashpur district is Mal (midland yellow-red soil), no irrigation. Should I do lehi sowing, and what about biasi?</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>65% chance: onset from 8 to 16 June.  
-In this case:
-- Do not plan lehi sowing.
-- Sow rainfed paddy from late June after steady rain.
-- Use biasi only for direct-seeded paddy, not transplanted paddy.
-15% chance: onset before 8 June.  
-In this case:
-- Do not rush after one shower; wait for continuous rain.
-- Prepare the nursery or field for normal sowing.
-- Lehi is unnecessary.
-20% chance: onset after 16 June.  
-In this case:
-- If rain settles by late June, transplant 15–20-day-old seedlings.
-- If delayed to mid-July, use sprouted seed under lehi with a medium-duration variety.
-- For direct-seeded paddy, use improved biasi and manage water carefully.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Jashpur / midland / No irrigation</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>• MTU-1010
-• PA-6444
-• PHB-71
-• KRH-1
-• Indirasona
-• Mahamaya
-• Danteswari
-• Karma masuri
-• Bambleswari
-• Sowing of sprouted rice seed under lehi condition
-• sowing of medium duration variety
-• proper water management
-• apply 15-20 kg ZnSO4 before planting
-• improved Biasi in direct seeded rice
-• As recommended
-• 15-20 kg ZnSO4/ha
-• Not specified
-• Seed drills under RKVY
-• seed supply through Seed corporation</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>• sowing of medium duration variety [~fuzzy]
-• Sowing of sprouted rice seed under lehi condition [~semantic]</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>• MTU-1010
-• PA-6444
-• PHB-71
-• KRH-1
-• Indirasona
-• Mahamaya
-• Danteswari
-• Karma masuri
-• Bambleswari
-• proper water management
-• apply 15-20 kg ZnSO4 before planting
-• improved Biasi in direct seeded rice
-• As recommended
-• 15-20 kg ZnSO4/ha
-• Not specified
-• Seed drills under RKVY
-• seed supply through Seed corporation</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Jashpur · rows 6</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>Delayed 4 weeks (July 2nd week)</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>English response (4 week delay)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>I am from Jashpur block, Jashpur district, my land is Gabhar lowland and I have canal/tube well irrigation. Canal water release is late this year. How should I transplant rice and manage irrigation?</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>70% chance: onset from 7 to 18 June.
-In this case:
-- Transplant by SRI only after steady rain or assured tube-well water.
-- Use tube-well water for establishment; use alternate-furrow irrigation where possible.
-- If canal delay continues and water is inadequate, use aerobic rice instead of transplanting.
-15% chance: onset before 7 June.
-In this case:
-- Do not transplant after one shower; wait for continuous rain.
-- Once water is assured, transplant by SRI and irrigate through alternate furrows.
-15% chance: onset after 18 June.
-In this case:
-- Delay transplanting until rain or tube-well supply is dependable.
-- If water remains limited, avoid puddled transplanting and use aerobic rice.
-- Reserve tube-well water for establishment and critical crop stages.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Jashpur / lowland / Irrigation available</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>• Wheat: GW-273
-• GW-173
-• DL-788-2
-• C-306
-• Mustard: Varun
-• Pusa Bold
-• Vardan
-• Krishna
-• Chickpea: JG-74
-• JG-315
-• Vaibhav
-• Rice transplanting by SRI system
-• alternate furrow irrigation
-• As recommended
-• Not specified
-• Seed supply through State seed corporation under RKVY
-• SRI system</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>• alternate furrow irrigation [~fuzzy]</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>• Wheat: GW-273
-• GW-173
-• DL-788-2
-• C-306
-• Mustard: Varun
-• Pusa Bold
-• Vardan
-• Krishna
-• Chickpea: JG-74
-• JG-315
-• Vaibhav
-• Rice transplanting by SRI system
-• As recommended
-• Not specified
-• Seed supply through State seed corporation under RKVY
-• SRI system</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Jashpur · rows 14</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Irrigated - Delayed release of water in canals</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>English response (normal onset)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>In Kunkuri, Jashpur district, I farm Marhan upland land with no irrigation. My crop is facing dry spell stress. What implements or help can I get and what should I do in the field?</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Marhan is upland. For your rainfed paddy:
-20% chance: onset before 8 June.  
-In this case:
-- Weed/interculture, thin crowded plants and fill gaps.
-- Open conservation furrows and use removed weeds as mulch.
-- Postpone top-dressing until rain resumes.
-60% chance: onset from 8 to 18 June.  
-In this case:
-- Conserve moisture now; wait for steady rain before filling gaps.
-- Re-sow only failed paddy patches after sufficient rain.
-- Ask the Agriculture Department about intercultural implements and seed support under RKVY.
-20% chance: onset after 18 June.  
-In this case:
-- Avoid fertilizer top-dressing during the dry spell.
-- Keep conservation furrows open; watch stressed paddy for pests and disease.
-- Ask locally about a farm pond under the IWSM programme and seed support if re-sowing is needed.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Jashpur / upland / No irrigation</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>• As per normal (no change recommended)
-• Intercultural operations
-• life saving irrigation
-• in situ soil water conservation measures
-• As recommended
-• Not specified
-• Supply of inter cultural implements under RKVY
-• seed supply through State seed corporation under RKVY</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>• Intercultural operations [~fuzzy]
-• Supply of inter cultural implements under RKVY [~semantic]
-• seed supply through State seed corporation under RKVY [~semantic]</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>• As per normal (no change recommended)
-• life saving irrigation
-• in situ soil water conservation measures
-• As recommended
-• Not specified</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Jashpur · rows 11</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Partial — some key advice missing</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Normal onset followed by 15-20 days dry spell</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>English response (normal onset)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>My Mal type field is in Pathalgaon, Jashpur district, no irrigation. Fields are drying up. Is there any life-saving step should I take?</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Is your “Mal” field considered high land, medium land, or low land locally?</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Jashpur / midland / No irrigation</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>• As per normal (no change recommended)
-• Life saving irrigation
-• in situ soil water conservation measures
-• As recommended
-• Not specified
-• Farm pond through IWSM programme</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>• As per normal (no change recommended)
-• Life saving irrigation
-• in situ soil water conservation measures
-• As recommended
-• Not specified
-• Farm pond through IWSM programme</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Jashpur · rows 12</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Normal onset followed by 15-20 days dry spell</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>English response (normal onset)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Odgi, Surajpur district — my land is Gabhar (lowland), no irrigation. Which dhan seed variety should I choose this year?</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>20% chance: onset before 10 June.  
-In this case:
-- Do not sow after one shower; wait for continuous rain.
-- Keep Swarna, Swarna Sub-1, Mahamaya or Jaldubi seed ready.
-- Transplant 15–20-day-old seedlings.
-65% chance: onset from 10 to 24 June.  
-In this case:
-- Best choices for your rainfed lowland: Swarna, Swarna Sub-1, Mahamaya, Jaldubi, Karma Mahsuri or Danteswari.
-- Raise a nursery and use 15–20-day-old seedlings.
-- Apply 15–20 kg zinc sulphate/ha before planting.
-15% chance: onset after 24 June.  
-In this case:
-- Up to 15 July, use the varieties listed above.
-- From 16–31 July, prefer short/medium-duration MTU-1010, PA-6444, Durgeshwari or Maheshwari.
-- For late onset, direct-seed sprouted dhan in puddled soil.</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Surajpur / lowland / No irrigation</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>• Sawarna
+• Karma Mahsuri
+• Swarna sub-1
+• Standard transplanting
+• recommended package
+• Recommended dose
+• Normal
 • Sawarna sub-1
-• MTU-1010
-• PA-6444
 • PHB-71
 • KRH-1
 • Indira sona
 • IGKV R2/Durgeshwari
 • IGKV R1244/Maheshwari
 • Grow short/medium-duration variety
-• direct seeding of sprouted rice seed under puddled condition
-• Recommended dose
-• Seed supply through corporation</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>• Sawarna [~fuzzy]
-• Sawarna sub-1 [~fuzzy]
-• MTU-1010
-• PA-6444
-• direct seeding of sprouted rice seed under puddled condition [~semantic]</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>• PHB-71
-• KRH-1
-• Indira sona
-• IGKV R2/Durgeshwari
-• IGKV R1244/Maheshwari
-• Grow short/medium-duration variety
-• Recommended dose
-• Seed supply through corporation</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Surajpur · rows 7</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Partial — some key advice missing</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Delayed 2 weeks (15 Jun-15 Jul)</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>English response (2 week delay)</t>
+• Seed supply through corporation
+• Purnima
+• Short-duration variety
+• weed mulching
+• biasi
+• foliar urea for established crops
+• Foliar urea if stress</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Surajpur · rows 4, 7, 9</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Low score — review chatbot response</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>In Pratappur, Surajpur district, I have Marhan land, no irrigation. Should I increase my seed rate and use sprouted seed for sowing rice?</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Marhan is high land. Do not increase seed rate now. Use sprouted seed with 20% extra seed only if monsoon onset is delayed to 16–31 July.
-15% chance: onset before 10 June.  
-In this case:
-- Wait for continuous rain; do not sow after one shower.
-- Use normal seed rate and line sowing.
-65% chance: onset from 10 to 24 June.  
-In this case:
-- Use normal seed rate and line sowing.
-- Suitable paddy varieties include Tulsi, Vandana, Anjali and Danteshwari.
-20% chance: onset after 24 June.  
-In this case:
-- If onset is by 15 July, use normal seed rate and line sowing.
-- If delayed to 16–31 July, direct-sow sprouted seed in puddled soil and increase seed rate by 20%.</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>I farm on Tikra land in Surajpur block, Surajpur district, no irrigation facility. My rice, arhar, maize all look stressed and are drying up. What should I do to save the crop, and is there any pond or water-saving structure I can get?</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>I can advise only on weather-informed paddy practices. For the other stressed crops, contact the nearest KVK or local agricultural office.
+70% chance: onset from 12 to 22 June.  
+In this case:
+- Weed and use weeds as mulch; lightly intercultivate to reduce moisture loss.
+- Open conservation furrows to catch rain.
+- After moisture returns, spray 2% urea on paddy.
+15% chance: onset before 12 June.  
+In this case:
+- Repair bunds and conservation furrows now.
+- Thin overcrowded paddy and fill small gaps after rain.
+- Apply 2% urea spray once plants recover.
+15% chance: onset after 22 June.  
+In this case:
+- Paddy on Tikra land faces high drying risk; thin plants and weed-mulch immediately.
+- Prioritise any available water for one life-saving irrigation.
+- Ask the Block Agriculture/Watershed Office about farm-pond assistance under the IWSM programme; confirm current eligibility locally.
+This is a proof-of-concept recommendation.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Surajpur / upland / No irrigation</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>No golden dataset match — No row matches (district + land type + irrigation + scenario)</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Delayed 4-6 weeks (16-31 Jul)</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>English response (4 week delay)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ramanujnagar, Surajpur district, my land is Marhan, no irrigation. Along with rice I also grow maize, arhar, urad, groundnut, til. Tell me what I should do for each crop given there has been no rainfall this season. </t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Marhan is high land. With no irrigation, do not sow paddy into dry soil.
-60% chance: onset from 10 to 24 June.
-In this case:
-- After steady rain begins, line-sow Tulsi, Vandana, Aditya, Kalinga-3, Vanprabha or Danteshwari.
-- Apply the locally recommended fertilizer dose.
-- Prepare bunds now to retain rainwater.
-20% chance: onset before 10 June.
-In this case:
-- Sow only after continuous rain has properly moistened the soil.
-- Use the same upland varieties and line sowing.
-- Repair bunds before sowing.
-20% chance: onset after 24 June.
-In this case:
-- Up to 15 July, line-sow the listed upland varieties after steady rain.
-- If delayed to 16–31 July, use Anjali, Poornima, Annada or Danteshwari; direct-sow sprouted seed in puddled soil.
-- Increase seed rate by 20% for this late sowing.
-This proof-of-concept covers only weather-informed paddy advice. For your other crops, contact the nearest KVK or local agricultural office.</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Surajpur / upland / No irrigation</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>• Rice: Tulsi
 • Vandana
@@ -1911,7 +1145,1302 @@
 • Sesame/Groundnut – line sowing
 • Recommended dose per crop
 • Atrazine @2 gm/L water (PE) for Maize
-• Line sowing with seed drills</t>
+• Line sowing with seed drills
+• Rice: Anjali
+• Purnima
+• Annada
+• Maize: Pro-4212
+• Pusa Early Makka-1
+• Vivek hybrid-9 &amp; 17
+• Moong: Pusa Vishal
+• BM-4
+• HUM-12
+• Pragya (rabi)
+• Pairi Moong (rabi)
+• Direct seeding of sprouted rice seed under puddled condition
+• 20% higher seed rate for rice
+• proper spacing + Rhizobium for pulses
+• Atrazine for Maize PE
+• Recommended dose
+• Seed supply through corporation
+• Existing varieties
+• Thinning and gap filling
+• re-sowing
+• sprouted seed if nursery unavailable
+• life-saving irrigation
+• in situ SWC
+• inter-cultural implements through RKVY
+• farm pond through IWSM</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>• life-saving irrigation</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>• Rice: Tulsi
+• Vandana
+• Aditya
+• Kalinga-3
+• Samleshwari
+• Vanprabha
+• Indira barani dhan-1
+• Anjali
+• Danteshwari
+• Pigeonpea: UPAS-120
+• TAG-10
+• Asha
+• Rajivlochan
+• ICPL-151
+• ICPL-87
+• Urd: JU-2
+• JU-3
+• PDU-1
+• TAU-2
+• TU-94-2
+• Maize: HISHELL
+• BIO-9681
+• DHM117
+• PMH-3
+• PRO-4640
+• PIO30-R26
+• Pro-4212
+• P-3785
+• 900M Gold
+• Groundnut: SB-11
+• JL-24
+• ICGS-11
+• ICGS-34
+• ICGS-43
+• Sesame: Selection-5
+• TC-25
+• JT-21
+• Line sowing with recommended fertilizer
+• Pigeonpea/Urd – proper spacing
+• Rhizobium culture
+• Maize – line sowing
+• Atrazine @2 gm/L water PE
+• Sesame/Groundnut – line sowing
+• Recommended dose per crop
+• Atrazine @2 gm/L water (PE) for Maize
+• Line sowing with seed drills
+• Rice: Anjali
+• Purnima
+• Annada
+• Maize: Pro-4212
+• Pusa Early Makka-1
+• Vivek hybrid-9 &amp; 17
+• Moong: Pusa Vishal
+• BM-4
+• HUM-12
+• Pragya (rabi)
+• Pairi Moong (rabi)
+• Direct seeding of sprouted rice seed under puddled condition
+• 20% higher seed rate for rice
+• proper spacing + Rhizobium for pulses
+• Atrazine for Maize PE
+• Recommended dose
+• Seed supply through corporation
+• Existing varieties
+• Thinning and gap filling
+• re-sowing
+• sprouted seed if nursery unavailable
+• in situ SWC
+• inter-cultural implements through RKVY
+• farm pond through IWSM</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Surajpur · rows 2, 5, 10</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Low score — review chatbot response</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>In Balrampur block, Balrampur district, my land is Mal type with no irrigation. Which dhan variety should I transplant this year and do I need to add some chemical?</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>I am treating “Mal” as medium land.
+60% chance: onset from 10 to 24 June.  
+In this case:
+- MTU-1010 is a practical choice; Purnima or Samleshwari are alternatives.
+- Raise nursery with steady rain; transplant 15–20-day seedlings.
+- Before planting, apply zinc sulphate 15–20 kg/ha plus the locally recommended fertilizer dose. Do not spray pesticide routinely.
+20% chance: onset before 10 June.  
+In this case:
+- Keep MTU-1010 seed ready, but do not act on one shower.
+- Transplant 15–20-day seedlings after dependable rain.
+- Use the same zinc treatment; ask Balrampur KVK for the exact fertilizer dose.
+20% chance: onset after 24 June.  
+In this case:
+- If rain starts by 15 July, transplant MTU-1010 with 15–20-day seedlings.
+- If it starts 16–31 July, avoid late transplanting; direct-seed sprouted MTU-1010 in puddled soil.
+- After 1 August, paddy risk rises sharply; use early-duration direct-seeded paddy and consult Balrampur KVK.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Balrampur / midland / No irrigation</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>• MTU-1010
+• PA-6444
+• PHB-71
+• KRH-1
+• Indira Sona
+• Purnima
+• Indira Barani Dhan-1
+• Samleshwari
+• IGKV R1
+• 15-20 days old seedling for transplanting
+• apply 15-20 kg ZnSO4 before planting
+• recommended dose of fertilizer
+• As recommended
+• 15-20 kg ZnSO4/ha
+• Not specified
+• Swarna
+• Grow short and medium duration variety
+• direct seeding of sprouted rice seed under puddled condition
+• Early and short duration varieties (unspecified)
+• Grow short duration variety
+• weed mulching
+• biasi and foliar urea if already sown
+• Foliar application of urea if already sown
+• PHB-71 (no change recommended)
+• Thinning and gap filling
+• re-sowing
+• sowing of sprouted seed if nursery unavailable
+• life saving irrigation
+• in situ SWC measures
+• in situ SWC</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>• MTU-1010
+• Purnima
+• Samleshwari
+• As recommended [~fuzzy]
+• 15-20 days old seedling for transplanting [~semantic]
+• apply 15-20 kg ZnSO4 before planting [~semantic]
+• recommended dose of fertilizer [~semantic]
+• sowing of sprouted seed if nursery unavailable [~semantic]</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>• PA-6444
+• PHB-71
+• KRH-1
+• Indira Sona
+• Indira Barani Dhan-1
+• IGKV R1
+• 15-20 kg ZnSO4/ha
+• Not specified
+• Swarna
+• Grow short and medium duration variety
+• direct seeding of sprouted rice seed under puddled condition
+• Early and short duration varieties (unspecified)
+• Grow short duration variety
+• weed mulching
+• biasi and foliar urea if already sown
+• Foliar application of urea if already sown
+• PHB-71 (no change recommended)
+• Thinning and gap filling
+• re-sowing
+• life saving irrigation
+• in situ SWC measures
+• in situ SWC</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Balrampur · rows 3, 6, 8, 11</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Low score — review chatbot response</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Ramanujganj, Balrampur district — my field is Gabhar, no irrigation. Which dhan variety is suitable for me this year?</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Your Gabhar field is classified as low land.
+20% chance: onset before 12 June.
+In this case:
+- Use Swarna, Swarna Sub-1, or Mahamaya.
+- Start nursery only after continuous rain begins.
+- Transplant 15–20-day-old seedlings.
+60% chance: onset from 12 to 22 June.
+In this case:
+- Swarna, Swarna Sub-1, Mahamaya, or Danteshwari are suitable.
+- Repair bunds to conserve rainwater.
+- Transplant 15–20-day-old seedlings.
+20% chance: onset after 22 June.
+In this case:
+- By 15 July: use the varieties above.
+- During 16–31 July: prefer MTU-1010, PA-6444, or Indira Sona; direct-sow sprouted seed in a puddled field.
+- During 1–15 August: prefer Purnima or MTU-1010; later onset makes rainfed paddy highly risky.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Balrampur / lowland / No irrigation</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>• Swarna
+• Jaldubi
+• PA-6444
+• Mahamaya
+• Danteshwari
+• Bamleshwari
+• Karma Mahsuri
+• Swarna sub-1
+• IGKV R2
+• IGKV R1244
+• As recommended (standard DACP guidelines)
+• As recommended
+• Not specified
+• MTU-1010
+• PHB-71
+• KRH-1
+• Indira Sona
+• Grow short and medium duration variety
+• direct seeding of sprouted rice seed under puddled condition
+• Purnima
+• Grow short duration variety
+• weed mulching
+• biasi and foliar urea if already sown
+• Foliar application of urea if already sown
+• Normal varieties (no change recommended)
+• Gap filling
+• life saving irrigation
+• in situ SWC measures
+• in situ SWC</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>• Swarna
+• PA-6444
+• Mahamaya
+• Danteshwari
+• Swarna sub-1
+• MTU-1010
+• Indira Sona
+• Purnima
+• Normal varieties (no change recommended) [~semantic]</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>• Jaldubi
+• Bamleshwari
+• Karma Mahsuri
+• IGKV R2
+• IGKV R1244
+• As recommended (standard DACP guidelines)
+• As recommended
+• Not specified
+• PHB-71
+• KRH-1
+• Grow short and medium duration variety
+• direct seeding of sprouted rice seed under puddled condition
+• Grow short duration variety
+• weed mulching
+• biasi and foliar urea if already sown
+• Foliar application of urea if already sown
+• Gap filling
+• life saving irrigation
+• in situ SWC measures
+• in situ SWC</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Balrampur · rows 4, 7, 9, 12</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Partial — some key advice missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>In Wadrafnagar, Balrampur district, I have Marhan upland, no irrigation source. What should I sow now and how?</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Your Marhan field is upland and rainfed.
+60% chance: onset from 10 June to 24 June.
+In this case:
+- After steady rain, line-sow paddy; do not sow on one shower.
+- From 15 June, use an upland variety such as Vandana, Anjali, Tulsi or Indira Barani Dhan-1.
+- Apply the locally recommended fertilizer dose.
+20% chance: onset before 10 June.
+In this case:
+- Prepare the field and moisture-conservation furrows.
+- Sow only after continuous rain starts.
+- Confirm variety timing with the nearest KVK because this early window is not covered by this PoC.
+20% chance: onset after 24 June.
+In this case:
+- By 15 July: line-sow the upland varieties listed above.
+- During 16–31 July: direct-sow sprouted Anjali, Purnima or Annda seed in puddled soil; increase seed rate by 20%.
+- After 31 July, unirrigated upland paddy is very risky; consult KVK before sowing.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Balrampur / upland / No irrigation</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>• Tulsi
+• Vandana
+• Aditya
+• Kalinga-3
+• Samleshwari
+• Vanprabha
+• Indira Barani Dhan-1
+• Anjali
+• Danteshwari
+• Line sowing with recommended dose of fertilizer
+• As recommended
+• Not specified
+• Purnima
+• Annada
+• Direct seeding of sprouted rice seed under puddled condition
+• increase seed rate by 20%
+• Local varieties (no change recommended)
+• Thinning and gap filling of existing crops
+• re-sowing
+• life saving irrigation
+• in situ SWC measures
+• supply of inter-cultural implements
+• farm pond via IWSM</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>• Tulsi
+• Vandana
+• Indira Barani Dhan-1
+• Anjali
+• As recommended [~fuzzy]
+• Purnima
+• Annada [~fuzzy]
+• increase seed rate by 20%
+• re-sowing [~fuzzy]
+• Line sowing with recommended dose of fertilizer [~semantic]
+• Direct seeding of sprouted rice seed under puddled condition [~semantic]</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>• Aditya
+• Kalinga-3
+• Samleshwari
+• Vanprabha
+• Danteshwari
+• Not specified
+• Local varieties (no change recommended)
+• Thinning and gap filling of existing crops
+• life saving irrigation
+• in situ SWC measures
+• supply of inter-cultural implements
+• farm pond via IWSM</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Balrampur · rows 2, 5, 10</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Partial — some key advice missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>My field in Bagicha, Jashpur district is Mal (midland yellow-red soil), no irrigation. Should I do lehi sowing, and what about biasi?</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>65% chance: onset from 8 to 16 June.  
+In this case:
+- Do not plan lehi sowing.
+- Sow rainfed paddy from late June after steady rain.
+- Use biasi only for direct-seeded paddy, not transplanted paddy.
+15% chance: onset before 8 June.  
+In this case:
+- Do not rush after one shower; wait for continuous rain.
+- Prepare the nursery or field for normal sowing.
+- Lehi is unnecessary.
+20% chance: onset after 16 June.  
+In this case:
+- If rain settles by late June, transplant 15–20-day-old seedlings.
+- If delayed to mid-July, use sprouted seed under lehi with a medium-duration variety.
+- For direct-seeded paddy, use improved biasi and manage water carefully.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Jashpur / midland / No irrigation</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>• MTU-1010
+• PA-6444
+• PHB-71
+• KRH-1
+• Indirasona
+• Mahamaya
+• Danteswari
+• Karma masuri
+• Bambleswari
+• Use 15-20 days old seedling for transplanting
+• apply 15-20 kg ZnSO4 before planting or sowing
+• recommended dose of fertilizer
+• As recommended
+• 15-20 kg ZnSO4/ha
+• Not specified
+• Sowing of sprouted rice seed under lehi condition
+• sowing of medium duration variety
+• proper water management
+• apply 15-20 kg ZnSO4 before planting
+• improved Biasi in direct seeded rice
+• Seed drills under RKVY
+• seed supply through Seed corporation
+• Indira sona
+• sowing of medium duration variety with 25% higher seed rate
+• As per normal (no change recommended)
+• Life saving irrigation
+• in situ soil water conservation measures
+• Farm pond through IWSM programme</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>• sowing of medium duration variety [~fuzzy]
+• Use 15-20 days old seedling for transplanting [~semantic]
+• Sowing of sprouted rice seed under lehi condition [~semantic]
+• sowing of medium duration variety with 25% higher seed rate [~semantic]</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>• MTU-1010
+• PA-6444
+• PHB-71
+• KRH-1
+• Indirasona
+• Mahamaya
+• Danteswari
+• Karma masuri
+• Bambleswari
+• apply 15-20 kg ZnSO4 before planting or sowing
+• recommended dose of fertilizer
+• As recommended
+• 15-20 kg ZnSO4/ha
+• Not specified
+• proper water management
+• apply 15-20 kg ZnSO4 before planting
+• improved Biasi in direct seeded rice
+• Seed drills under RKVY
+• seed supply through Seed corporation
+• Indira sona
+• As per normal (no change recommended)
+• Life saving irrigation
+• in situ soil water conservation measures
+• Farm pond through IWSM programme</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Jashpur · rows 3, 6, 8, 12</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Low score — review chatbot response</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>I am from Jashpur block, Jashpur district, my land is Gabhar lowland and I have canal/tube well irrigation. Canal water release is late this year. How should I transplant rice and manage irrigation?</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>70% chance: onset from 7 to 18 June.
+In this case:
+- Transplant by SRI only after steady rain or assured tube-well water.
+- Use tube-well water for establishment; use alternate-furrow irrigation where possible.
+- If canal delay continues and water is inadequate, use aerobic rice instead of transplanting.
+15% chance: onset before 7 June.
+In this case:
+- Do not transplant after one shower; wait for continuous rain.
+- Once water is assured, transplant by SRI and irrigate through alternate furrows.
+15% chance: onset after 18 June.
+In this case:
+- Delay transplanting until rain or tube-well supply is dependable.
+- If water remains limited, avoid puddled transplanting and use aerobic rice.
+- Reserve tube-well water for establishment and critical crop stages.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Jashpur / lowland / Irrigation available</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>• Wheat: GW-273
+• GW-173
+• DL-788-2
+• C-306
+• Mustard: Varun
+• Pusa Bold
+• Vardan
+• Krishna
+• Chickpea: JG-74
+• JG-315
+• Vaibhav
+• Rice transplanting by SRI system
+• alternate furrow irrigation
+• As recommended
+• Not specified
+• Seed supply through State seed corporation under RKVY
+• SRI system
+• irrigate crops by sprinkler
+• Sprinkler irrigation</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>• alternate furrow irrigation [~fuzzy]
+• irrigate crops by sprinkler [~semantic]
+• Sprinkler irrigation [~semantic]</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>• Wheat: GW-273
+• GW-173
+• DL-788-2
+• C-306
+• Mustard: Varun
+• Pusa Bold
+• Vardan
+• Krishna
+• Chickpea: JG-74
+• JG-315
+• Vaibhav
+• Rice transplanting by SRI system
+• As recommended
+• Not specified
+• Seed supply through State seed corporation under RKVY
+• SRI system</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Jashpur · rows 14, 15</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Low score — review chatbot response</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>In Kunkuri, Jashpur district, I farm Marhan upland land with no irrigation. My crop is facing dry spell stress. What implements or help can I get and what should I do in the field?</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Marhan is upland. For your rainfed paddy:
+20% chance: onset before 8 June.  
+In this case:
+- Weed/interculture, thin crowded plants and fill gaps.
+- Open conservation furrows and use removed weeds as mulch.
+- Postpone top-dressing until rain resumes.
+60% chance: onset from 8 to 18 June.  
+In this case:
+- Conserve moisture now; wait for steady rain before filling gaps.
+- Re-sow only failed paddy patches after sufficient rain.
+- Ask the Agriculture Department about intercultural implements and seed support under RKVY.
+20% chance: onset after 18 June.  
+In this case:
+- Avoid fertilizer top-dressing during the dry spell.
+- Keep conservation furrows open; watch stressed paddy for pests and disease.
+- Ask locally about a farm pond under the IWSM programme and seed support if re-sowing is needed.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Jashpur / upland / No irrigation</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>• Tulsi
+• Aditya
+• Kalinga-3
+• Samleswari
+• Vandana
+• Vanprabha
+• Line sowing with recommended dose of fertilizer
+• As recommended
+• Not specified
+• Seed drills provided under RKVY
+• seed supply through Seed corporation/Agril Department
+• As per normal (no change recommended)
+• Intercultural operations
+• life saving irrigation
+• in situ soil water conservation measures
+• Supply of inter cultural implements under RKVY
+• seed supply through State seed corporation under RKVY</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>• Intercultural operations [~fuzzy]
+• seed supply through Seed corporation/Agril Department [~semantic]
+• Supply of inter cultural implements under RKVY [~semantic]
+• seed supply through State seed corporation under RKVY [~semantic]</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>• Tulsi
+• Aditya
+• Kalinga-3
+• Samleswari
+• Vandana
+• Vanprabha
+• Line sowing with recommended dose of fertilizer
+• As recommended
+• Not specified
+• Seed drills provided under RKVY
+• As per normal (no change recommended)
+• life saving irrigation
+• in situ soil water conservation measures</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Jashpur · rows 2, 5, 11</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Low score — review chatbot response</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>My Mal type field is in Pathalgaon, Jashpur district, no irrigation. Fields are drying up. Is there any life-saving step should I take?</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Is your “Mal” field considered high land, medium land, or low land locally?</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Jashpur / midland / No irrigation</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>• MTU-1010
+• PA-6444
+• PHB-71
+• KRH-1
+• Indirasona
+• Mahamaya
+• Danteswari
+• Karma masuri
+• Bambleswari
+• Use 15-20 days old seedling for transplanting
+• apply 15-20 kg ZnSO4 before planting or sowing
+• recommended dose of fertilizer
+• As recommended
+• 15-20 kg ZnSO4/ha
+• Not specified
+• Sowing of sprouted rice seed under lehi condition
+• sowing of medium duration variety
+• proper water management
+• apply 15-20 kg ZnSO4 before planting
+• improved Biasi in direct seeded rice
+• Seed drills under RKVY
+• seed supply through Seed corporation
+• Indira sona
+• sowing of medium duration variety with 25% higher seed rate
+• As per normal (no change recommended)
+• Life saving irrigation
+• in situ soil water conservation measures
+• Farm pond through IWSM programme</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>• MTU-1010
+• PA-6444
+• PHB-71
+• KRH-1
+• Indirasona
+• Mahamaya
+• Danteswari
+• Karma masuri
+• Bambleswari
+• Use 15-20 days old seedling for transplanting
+• apply 15-20 kg ZnSO4 before planting or sowing
+• recommended dose of fertilizer
+• As recommended
+• 15-20 kg ZnSO4/ha
+• Not specified
+• Sowing of sprouted rice seed under lehi condition
+• sowing of medium duration variety
+• proper water management
+• apply 15-20 kg ZnSO4 before planting
+• improved Biasi in direct seeded rice
+• Seed drills under RKVY
+• seed supply through Seed corporation
+• Indira sona
+• sowing of medium duration variety with 25% higher seed rate
+• As per normal (no change recommended)
+• Life saving irrigation
+• in situ soil water conservation measures
+• Farm pond through IWSM programme</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Jashpur · rows 3, 6, 8, 12</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Low score — review chatbot response</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Odgi, Surajpur district — my land is Gabhar (lowland), no irrigation. Which dhan seed variety should I choose this year?</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>20% chance: onset before 10 June.  
+In this case:
+- Do not sow after one shower; wait for continuous rain.
+- Keep Swarna, Swarna Sub-1, Mahamaya or Jaldubi seed ready.
+- Transplant 15–20-day-old seedlings.
+65% chance: onset from 10 to 24 June.  
+In this case:
+- Best choices for your rainfed lowland: Swarna, Swarna Sub-1, Mahamaya, Jaldubi, Karma Mahsuri or Danteswari.
+- Raise a nursery and use 15–20-day-old seedlings.
+- Apply 15–20 kg zinc sulphate/ha before planting.
+15% chance: onset after 24 June.  
+In this case:
+- Up to 15 July, use the varieties listed above.
+- From 16–31 July, prefer short/medium-duration MTU-1010, PA-6444, Durgeshwari or Maheshwari.
+- For late onset, direct-seed sprouted dhan in puddled soil.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Surajpur / lowland / No irrigation</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>• Sawarna
+• Jaldubi
+• PA-6444
+• Mahamaya
+• Danteshwari
+• Bambleswari
+• Karma Mahsuri
+• Swarna sub-1
+• Standard transplanting
+• recommended package
+• Recommended dose
+• Normal
+• Sawarna sub-1
+• MTU-1010
+• PHB-71
+• KRH-1
+• Indira sona
+• IGKV R2/Durgeshwari
+• IGKV R1244/Maheshwari
+• Grow short/medium-duration variety
+• direct seeding of sprouted rice seed under puddled condition
+• Seed supply through corporation
+• Purnima
+• MTU-1010 (early + mid-early duration)
+• Short-duration variety
+• sprouted seed under puddled condition
+• weed mulching
+• biasi
+• foliar urea for established crops
+• Foliar urea if stress
+• Seed supply</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>• Sawarna [~fuzzy]
+• Jaldubi
+• PA-6444
+• Mahamaya
+• Danteshwari [~fuzzy]
+• Karma Mahsuri
+• Swarna sub-1
+• Sawarna sub-1 [~fuzzy]
+• MTU-1010
+• MTU-1010 (early + mid-early duration) [name match]
+• direct seeding of sprouted rice seed under puddled condition [~semantic]
+• sprouted seed under puddled condition [~semantic]
+• Seed supply [~semantic]</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>• Bambleswari
+• Standard transplanting
+• recommended package
+• Recommended dose
+• Normal
+• PHB-71
+• KRH-1
+• Indira sona
+• IGKV R2/Durgeshwari
+• IGKV R1244/Maheshwari
+• Grow short/medium-duration variety
+• Seed supply through corporation
+• Purnima
+• Short-duration variety
+• weed mulching
+• biasi
+• foliar urea for established crops
+• Foliar urea if stress</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Surajpur · rows 4, 7, 9</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Partial — some key advice missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>In Pratappur, Surajpur district, I have Marhan land, no irrigation. Should I increase my seed rate and use sprouted seed for sowing rice?</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Marhan is high land. Do not increase seed rate now. Use sprouted seed with 20% extra seed only if monsoon onset is delayed to 16–31 July.
+15% chance: onset before 10 June.  
+In this case:
+- Wait for continuous rain; do not sow after one shower.
+- Use normal seed rate and line sowing.
+65% chance: onset from 10 to 24 June.  
+In this case:
+- Use normal seed rate and line sowing.
+- Suitable paddy varieties include Tulsi, Vandana, Anjali and Danteshwari.
+20% chance: onset after 24 June.  
+In this case:
+- If onset is by 15 July, use normal seed rate and line sowing.
+- If delayed to 16–31 July, direct-sow sprouted seed in puddled soil and increase seed rate by 20%.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Surajpur / upland / No irrigation</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>• Rice: Tulsi
+• Vandana
+• Aditya
+• Kalinga-3
+• Samleshwari
+• Vanprabha
+• Indira barani dhan-1
+• Anjali
+• Danteshwari
+• Pigeonpea: UPAS-120
+• TAG-10
+• Asha
+• Rajivlochan
+• ICPL-151
+• ICPL-87
+• Urd: JU-2
+• JU-3
+• PDU-1
+• TAU-2
+• TU-94-2
+• Maize: HISHELL
+• BIO-9681
+• DHM117
+• PMH-3
+• PRO-4640
+• PIO30-R26
+• Pro-4212
+• P-3785
+• 900M Gold
+• Groundnut: SB-11
+• JL-24
+• ICGS-11
+• ICGS-34
+• ICGS-43
+• Sesame: Selection-5
+• TC-25
+• JT-21
+• Line sowing with recommended fertilizer
+• Pigeonpea/Urd – proper spacing
+• Rhizobium culture
+• Maize – line sowing
+• Atrazine @2 gm/L water PE
+• Sesame/Groundnut – line sowing
+• Recommended dose per crop
+• Atrazine @2 gm/L water (PE) for Maize
+• Line sowing with seed drills
+• Rice: Anjali
+• Purnima
+• Annada
+• Maize: Pro-4212
+• Pusa Early Makka-1
+• Vivek hybrid-9 &amp; 17
+• Moong: Pusa Vishal
+• BM-4
+• HUM-12
+• Pragya (rabi)
+• Pairi Moong (rabi)
+• Direct seeding of sprouted rice seed under puddled condition
+• 20% higher seed rate for rice
+• proper spacing + Rhizobium for pulses
+• Atrazine for Maize PE
+• Recommended dose
+• Seed supply through corporation
+• Existing varieties
+• Thinning and gap filling
+• re-sowing
+• sprouted seed if nursery unavailable
+• life-saving irrigation
+• in situ SWC
+• inter-cultural implements through RKVY
+• farm pond through IWSM</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>• Vandana
+• Anjali
+• Danteshwari
+• Asha [~fuzzy]
+• Maize – line sowing [~fuzzy]
+• re-sowing [~fuzzy]
+• Line sowing with recommended fertilizer [~semantic]
+• Line sowing with seed drills [~semantic]
+• Direct seeding of sprouted rice seed under puddled condition [~semantic]
+• 20% higher seed rate for rice [~semantic]
+• sprouted seed if nursery unavailable [~semantic]</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>• Rice: Tulsi
+• Aditya
+• Kalinga-3
+• Samleshwari
+• Vanprabha
+• Indira barani dhan-1
+• Pigeonpea: UPAS-120
+• TAG-10
+• Rajivlochan
+• ICPL-151
+• ICPL-87
+• Urd: JU-2
+• JU-3
+• PDU-1
+• TAU-2
+• TU-94-2
+• Maize: HISHELL
+• BIO-9681
+• DHM117
+• PMH-3
+• PRO-4640
+• PIO30-R26
+• Pro-4212
+• P-3785
+• 900M Gold
+• Groundnut: SB-11
+• JL-24
+• ICGS-11
+• ICGS-34
+• ICGS-43
+• Sesame: Selection-5
+• TC-25
+• JT-21
+• Pigeonpea/Urd – proper spacing
+• Rhizobium culture
+• Atrazine @2 gm/L water PE
+• Sesame/Groundnut – line sowing
+• Recommended dose per crop
+• Atrazine @2 gm/L water (PE) for Maize
+• Rice: Anjali
+• Purnima
+• Annada
+• Maize: Pro-4212
+• Pusa Early Makka-1
+• Vivek hybrid-9 &amp; 17
+• Moong: Pusa Vishal
+• BM-4
+• HUM-12
+• Pragya (rabi)
+• Pairi Moong (rabi)
+• proper spacing + Rhizobium for pulses
+• Atrazine for Maize PE
+• Recommended dose
+• Seed supply through corporation
+• Existing varieties
+• Thinning and gap filling
+• life-saving irrigation
+• in situ SWC
+• inter-cultural implements through RKVY
+• farm pond through IWSM</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Surajpur · rows 2, 5, 10</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Low score — review chatbot response</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ramanujnagar, Surajpur district, my land is Marhan, no irrigation. Along with rice I also grow maize, arhar, urad, groundnut, til. Tell me what I should do for each crop given there has been no rainfall this season. </t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Marhan is high land. With no irrigation, do not sow paddy into dry soil.
+60% chance: onset from 10 to 24 June.
+In this case:
+- After steady rain begins, line-sow Tulsi, Vandana, Aditya, Kalinga-3, Vanprabha or Danteshwari.
+- Apply the locally recommended fertilizer dose.
+- Prepare bunds now to retain rainwater.
+20% chance: onset before 10 June.
+In this case:
+- Sow only after continuous rain has properly moistened the soil.
+- Use the same upland varieties and line sowing.
+- Repair bunds before sowing.
+20% chance: onset after 24 June.
+In this case:
+- Up to 15 July, line-sow the listed upland varieties after steady rain.
+- If delayed to 16–31 July, use Anjali, Poornima, Annada or Danteshwari; direct-sow sprouted seed in puddled soil.
+- Increase seed rate by 20% for this late sowing.
+This proof-of-concept covers only weather-informed paddy advice. For your other crops, contact the nearest KVK or local agricultural office.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Surajpur / upland / No irrigation</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>• Rice: Tulsi
+• Vandana
+• Aditya
+• Kalinga-3
+• Samleshwari
+• Vanprabha
+• Indira barani dhan-1
+• Anjali
+• Danteshwari
+• Pigeonpea: UPAS-120
+• TAG-10
+• Asha
+• Rajivlochan
+• ICPL-151
+• ICPL-87
+• Urd: JU-2
+• JU-3
+• PDU-1
+• TAU-2
+• TU-94-2
+• Maize: HISHELL
+• BIO-9681
+• DHM117
+• PMH-3
+• PRO-4640
+• PIO30-R26
+• Pro-4212
+• P-3785
+• 900M Gold
+• Groundnut: SB-11
+• JL-24
+• ICGS-11
+• ICGS-34
+• ICGS-43
+• Sesame: Selection-5
+• TC-25
+• JT-21
+• Line sowing with recommended fertilizer
+• Pigeonpea/Urd – proper spacing
+• Rhizobium culture
+• Maize – line sowing
+• Atrazine @2 gm/L water PE
+• Sesame/Groundnut – line sowing
+• Recommended dose per crop
+• Atrazine @2 gm/L water (PE) for Maize
+• Line sowing with seed drills
+• Rice: Anjali
+• Purnima
+• Annada
+• Maize: Pro-4212
+• Pusa Early Makka-1
+• Vivek hybrid-9 &amp; 17
+• Moong: Pusa Vishal
+• BM-4
+• HUM-12
+• Pragya (rabi)
+• Pairi Moong (rabi)
+• Direct seeding of sprouted rice seed under puddled condition
+• 20% higher seed rate for rice
+• proper spacing + Rhizobium for pulses
+• Atrazine for Maize PE
+• Recommended dose
+• Seed supply through corporation
+• Existing varieties
+• Thinning and gap filling
+• re-sowing
+• sprouted seed if nursery unavailable
+• life-saving irrigation
+• in situ SWC
+• inter-cultural implements through RKVY
+• farm pond through IWSM</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1924,9 +2453,13 @@
 • Danteshwari
 • Asha [~fuzzy]
 • Maize – line sowing [~fuzzy]
+• Annada
+• Recommended dose [~fuzzy]
+• re-sowing [~fuzzy]
 • Line sowing with recommended fertilizer [~semantic]
 • Recommended dose per crop [~semantic]
-• Line sowing with seed drills [~semantic]</t>
+• Line sowing with seed drills [~semantic]
+• 20% higher seed rate for rice [~semantic]</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1965,30 +2498,41 @@
 • Rhizobium culture
 • Atrazine @2 gm/L water PE
 • Sesame/Groundnut – line sowing
-• Atrazine @2 gm/L water (PE) for Maize</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>23.9</v>
+• Atrazine @2 gm/L water (PE) for Maize
+• Rice: Anjali
+• Purnima
+• Maize: Pro-4212
+• Pusa Early Makka-1
+• Vivek hybrid-9 &amp; 17
+• Moong: Pusa Vishal
+• BM-4
+• HUM-12
+• Pragya (rabi)
+• Pairi Moong (rabi)
+• Direct seeding of sprouted rice seed under puddled condition
+• proper spacing + Rhizobium for pulses
+• Atrazine for Maize PE
+• Seed supply through corporation
+• Existing varieties
+• Thinning and gap filling
+• sprouted seed if nursery unavailable
+• life-saving irrigation
+• in situ SWC
+• inter-cultural implements through RKVY
+• farm pond through IWSM</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Surajpur · rows 2</t>
+          <t>Surajpur · rows 2, 5, 10</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Normal onset (15 Jun-15 Jul)</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>English response (normal onset)</t>
         </is>
       </c>
     </row>
@@ -2027,61 +2571,85 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>• Sawarna
-• MTU-1010
+          <t>• MTU-1010
 • PA-6444
 • PHB-71
 • KRH-1
 • Indira sona
+• Purnima
+• Indira barani dhan-1
+• Danteshwari
 • IGKV R1
+• Use 15-20 day old seedlings for transplanting
+• apply 15-20 kg ZnSO4 before planting
+• apply recommended fertilizer
+• Recommended dose + 15-20 kg ZnSO4/ha
+• ZnSO4 @15-20 kg/ha
+• ZnSO4 supply
+• Sawarna
 • Samleshwari
 • Grow short/medium-duration variety
 • direct seeding of sprouted rice seed under puddled condition
 • Recommended dose
-• Seed supply through corporation</t>
+• Seed supply through corporation
+• Early variety (short duration)
+• Grow short-duration variety
+• direct seeding of sprouted seed under puddled condition
+• weed mulching
+• biasi
+• foliar application of urea for established crops
+• Foliar urea if stress
+• Seed supply</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>• Recommended dose [~fuzzy]
-• direct seeding of sprouted rice seed under puddled condition [~semantic]</t>
+          <t>• Danteshwari
+• apply recommended fertilizer [~fuzzy]
+• Recommended dose [~fuzzy]
+• direct seeding of sprouted rice seed under puddled condition [~semantic]
+• direct seeding of sprouted seed under puddled condition [~semantic]
+• Seed supply [~semantic]</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>• Sawarna
-• MTU-1010
+          <t>• MTU-1010
 • PA-6444
 • PHB-71
 • KRH-1
 • Indira sona
+• Purnima
+• Indira barani dhan-1
 • IGKV R1
+• Use 15-20 day old seedlings for transplanting
+• apply 15-20 kg ZnSO4 before planting
+• Recommended dose + 15-20 kg ZnSO4/ha
+• ZnSO4 @15-20 kg/ha
+• ZnSO4 supply
+• Sawarna
 • Samleshwari
 • Grow short/medium-duration variety
-• Seed supply through corporation</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>16.7</v>
+• Seed supply through corporation
+• Early variety (short duration)
+• Grow short-duration variety
+• weed mulching
+• biasi
+• foliar application of urea for established crops
+• Foliar urea if stress</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Surajpur · rows 6</t>
+          <t>Surajpur · rows 3, 6, 8</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>Delayed 2-4 weeks (16-31 Jul)</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>English response (2 week delay)</t>
         </is>
       </c>
     </row>
@@ -2122,53 +2690,85 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>• Purnima
+          <t>• Swarna
+• Jaldubi
+• PA-6444
+• Mahamaya
+• Danteshwari
+• Bamleshwari
+• Karma Mahsuri
+• Swarna sub-1
+• IGKV R2
+• IGKV R1244
+• As recommended (standard DACP guidelines)
+• As recommended
+• Not specified
 • MTU-1010
+• PHB-71
+• KRH-1
+• Indira Sona
+• Grow short and medium duration variety
+• direct seeding of sprouted rice seed under puddled condition
+• Purnima
 • Grow short duration variety
-• direct seeding of sprouted rice seed under puddled condition
 • weed mulching
 • biasi and foliar urea if already sown
 • Foliar application of urea if already sown
-• Not specified</t>
+• Normal varieties (no change recommended)
+• Gap filling
+• life saving irrigation
+• in situ SWC measures
+• in situ SWC</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>• Purnima
+          <t>• Swarna
+• Jaldubi
+• PA-6444
+• Mahamaya
+• Swarna sub-1
 • MTU-1010
+• Purnima
 • weed mulching [~fuzzy]
 • direct seeding of sprouted rice seed under puddled condition [~semantic]</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>• Grow short duration variety
+          <t>• Danteshwari
+• Bamleshwari
+• Karma Mahsuri
+• IGKV R2
+• IGKV R1244
+• As recommended (standard DACP guidelines)
+• As recommended
+• Not specified
+• PHB-71
+• KRH-1
+• Indira Sona
+• Grow short and medium duration variety
+• Grow short duration variety
 • biasi and foliar urea if already sown
 • Foliar application of urea if already sown
-• Not specified</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>50</v>
+• Normal varieties (no change recommended)
+• Gap filling
+• life saving irrigation
+• in situ SWC measures
+• in situ SWC</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>31</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Balrampur · rows 9</t>
+          <t>Balrampur · rows 4, 7, 9, 12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Partial — some key advice missing</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Delayed 6-8 weeks (1-15 Aug)</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>English response (6 week delay)</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2807,22 @@
 • recommended dose of fertilizer
 • As recommended
 • 15-20 kg ZnSO4/ha
-• Not specified</t>
+• Not specified
+• Swarna
+• Grow short and medium duration variety
+• direct seeding of sprouted rice seed under puddled condition
+• Early and short duration varieties (unspecified)
+• Grow short duration variety
+• weed mulching
+• biasi and foliar urea if already sown
+• Foliar application of urea if already sown
+• PHB-71 (no change recommended)
+• Thinning and gap filling
+• re-sowing
+• sowing of sprouted seed if nursery unavailable
+• life saving irrigation
+• in situ SWC measures
+• in situ SWC</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
@@ -2227,30 +2842,35 @@
 • recommended dose of fertilizer
 • As recommended
 • 15-20 kg ZnSO4/ha
-• Not specified</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n">
+• Not specified
+• Swarna
+• Grow short and medium duration variety
+• direct seeding of sprouted rice seed under puddled condition
+• Early and short duration varieties (unspecified)
+• Grow short duration variety
+• weed mulching
+• biasi and foliar urea if already sown
+• Foliar application of urea if already sown
+• PHB-71 (no change recommended)
+• Thinning and gap filling
+• re-sowing
+• sowing of sprouted seed if nursery unavailable
+• life saving irrigation
+• in situ SWC measures
+• in situ SWC</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Balrampur · rows 3</t>
+          <t>Balrampur · rows 3, 6, 8, 11</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Delayed 2 weeks (15 Jun-15 Jul)</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>English response (2 week delay)</t>
         </is>
       </c>
     </row>
@@ -2276,48 +2896,82 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>• Normal varieties (no change recommended)
+          <t>• Swarna
+• Jaldubi
+• PA-6444
+• Mahamaya
+• Danteshwari
+• Bamleshwari
+• Karma Mahsuri
+• Swarna sub-1
+• IGKV R2
+• IGKV R1244
+• As recommended (standard DACP guidelines)
+• As recommended
+• Not specified
+• MTU-1010
+• PHB-71
+• KRH-1
+• Indira Sona
+• Grow short and medium duration variety
+• direct seeding of sprouted rice seed under puddled condition
+• Purnima
+• Grow short duration variety
+• weed mulching
+• biasi and foliar urea if already sown
+• Foliar application of urea if already sown
+• Normal varieties (no change recommended)
 • Gap filling
 • life saving irrigation
 • in situ SWC measures
+• in situ SWC</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>• Swarna
+• Jaldubi
+• PA-6444
+• Mahamaya
+• Danteshwari
+• Bamleshwari
+• Karma Mahsuri
+• Swarna sub-1
+• IGKV R2
+• IGKV R1244
+• As recommended (standard DACP guidelines)
 • As recommended
 • Not specified
-• in situ SWC</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>• Normal varieties (no change recommended)
+• MTU-1010
+• PHB-71
+• KRH-1
+• Indira Sona
+• Grow short and medium duration variety
+• direct seeding of sprouted rice seed under puddled condition
+• Purnima
+• Grow short duration variety
+• weed mulching
+• biasi and foliar urea if already sown
+• Foliar application of urea if already sown
+• Normal varieties (no change recommended)
 • Gap filling
 • life saving irrigation
 • in situ SWC measures
-• As recommended
-• Not specified
 • in situ SWC</t>
         </is>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Balrampur · rows 12</t>
+          <t>Balrampur · rows 4, 7, 9, 12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Normal onset followed by 15-20 days dry spell</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>English response (normal onset)</t>
         </is>
       </c>
     </row>
@@ -2371,7 +3025,10 @@
 • Shital
 • As recommended (standard DACP guidelines)
 • As recommended
-• Not specified</t>
+• Not specified
+• Seed supply through Seed corporation
+• As per normal varieties (no change specified)
+• As per normal (no change recommended)</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2379,7 +3036,8 @@
           <t>• Swarna
 • Swarna sub-1
 • Mahamaya
-• Danteswari</t>
+• Danteswari
+• Seed supply through Seed corporation [~semantic]</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2393,30 +3051,22 @@
 • Shital
 • As recommended (standard DACP guidelines)
 • As recommended
-• Not specified</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>28.6</v>
+• Not specified
+• As per normal varieties (no change specified)
+• As per normal (no change recommended)</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>29.4</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Jashpur · rows 4</t>
+          <t>Jashpur · rows 4, 7, 9, 10, 13</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>Delayed 2 weeks (June 4th week)</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>English response (2 week delay)</t>
         </is>
       </c>
     </row>
@@ -2467,17 +3117,20 @@
 • Chickpea: JG-74
 • JG-315
 • Vaibhav
-• Alternate furrow irrigation
-• irrigate crops by sprinkler
+• Rice transplanting by SRI system
+• alternate furrow irrigation
 • As recommended
 • Not specified
-• Sprinkler irrigation
-• seed supply through State seed corporation under RKVY</t>
+• Seed supply through State seed corporation under RKVY
+• SRI system
+• irrigate crops by sprinkler
+• Sprinkler irrigation</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>• Alternate furrow irrigation [~fuzzy]
+          <t>• alternate furrow irrigation [~fuzzy]
+• Rice transplanting by SRI system [~semantic]
 • irrigate crops by sprinkler [~semantic]
 • Sprinkler irrigation [~semantic]</t>
         </is>
@@ -2497,30 +3150,21 @@
 • Vaibhav
 • As recommended
 • Not specified
-• seed supply through State seed corporation under RKVY</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>17.6</v>
+• Seed supply through State seed corporation under RKVY
+• SRI system</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Jashpur · rows 15</t>
+          <t>Jashpur · rows 14, 15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Irrigated - Non-release of water in canals</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>English response (normal onset)</t>
         </is>
       </c>
     </row>
@@ -2563,28 +3207,39 @@
 • PA-6444
 • PHB-71
 • KRH-1
-• Indira sona
+• Indirasona
 • Mahamaya
 • Danteswari
 • Karma masuri
 • Bambleswari
-• Sowing of sprouted rice seed under lehi condition
-• sowing of medium duration variety with 25% higher seed rate
-• proper water management
-• apply 15-20 kg ZnSO4 before planting
+• Use 15-20 days old seedling for transplanting
+• apply 15-20 kg ZnSO4 before planting or sowing
+• recommended dose of fertilizer
 • As recommended
 • 15-20 kg ZnSO4/ha
 • Not specified
+• Sowing of sprouted rice seed under lehi condition
+• sowing of medium duration variety
+• proper water management
+• apply 15-20 kg ZnSO4 before planting
+• improved Biasi in direct seeded rice
 • Seed drills under RKVY
-• seed supply through Seed corporation</t>
+• seed supply through Seed corporation
+• Indira sona
+• sowing of medium duration variety with 25% higher seed rate
+• As per normal (no change recommended)
+• Life saving irrigation
+• in situ soil water conservation measures
+• Farm pond through IWSM programme</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>• Sowing of sprouted rice seed under lehi condition [~semantic]
-• sowing of medium duration variety with 25% higher seed rate [~semantic]
+          <t>• apply 15-20 kg ZnSO4 before planting or sowing [~semantic]
+• 15-20 kg ZnSO4/ha [~semantic]
+• Sowing of sprouted rice seed under lehi condition [~semantic]
 • apply 15-20 kg ZnSO4 before planting [~semantic]
-• 15-20 kg ZnSO4/ha [~semantic]</t>
+• sowing of medium duration variety with 25% higher seed rate [~semantic]</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2593,39 +3248,38 @@
 • PA-6444
 • PHB-71
 • KRH-1
-• Indira sona
+• Indirasona
 • Mahamaya
 • Danteswari
 • Karma masuri
 • Bambleswari
-• proper water management
+• Use 15-20 days old seedling for transplanting
+• recommended dose of fertilizer
 • As recommended
 • Not specified
+• sowing of medium duration variety
+• proper water management
+• improved Biasi in direct seeded rice
 • Seed drills under RKVY
-• seed supply through Seed corporation</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>22.2</v>
+• seed supply through Seed corporation
+• Indira sona
+• As per normal (no change recommended)
+• Life saving irrigation
+• in situ soil water conservation measures
+• Farm pond through IWSM programme</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Jashpur · rows 8</t>
+          <t>Jashpur · rows 3, 6, 8, 12</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Delayed 6 weeks (July 4th week)</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>English response (6 week delay)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +3330,13 @@
 • As recommended
 • Not specified
 • Seed drills provided under RKVY
-• seed supply through Seed corporation/Agril Department</t>
+• seed supply through Seed corporation/Agril Department
+• As per normal (no change recommended)
+• Intercultural operations
+• life saving irrigation
+• in situ soil water conservation measures
+• Supply of inter cultural implements under RKVY
+• seed supply through State seed corporation under RKVY</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2689,32 +3349,32 @@
 • Vanprabha
 • Seed drills provided under RKVY [~fuzzy]
 • Line sowing with recommended dose of fertilizer [~semantic]
-• seed supply through Seed corporation/Agril Department [~semantic]</t>
+• seed supply through Seed corporation/Agril Department [~semantic]
+• seed supply through State seed corporation under RKVY [~semantic]</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>• As recommended
-• Not specified</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="n">
-        <v>81.8</v>
+• Not specified
+• As per normal (no change recommended)
+• Intercultural operations
+• life saving irrigation
+• in situ soil water conservation measures
+• Supply of inter cultural implements under RKVY</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>58.8</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Jashpur · rows 5</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Delayed 4 weeks (July 2nd week)</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>English response (4 week delay)</t>
+          <t>Jashpur · rows 2, 5, 11</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Partial — some key advice missing</t>
         </is>
       </c>
     </row>
@@ -2767,14 +3427,29 @@
 • apply recommended fertilizer
 • Recommended dose + 15-20 kg ZnSO4/ha
 • ZnSO4 @15-20 kg/ha
-• ZnSO4 supply</t>
+• ZnSO4 supply
+• Sawarna
+• Samleshwari
+• Grow short/medium-duration variety
+• direct seeding of sprouted rice seed under puddled condition
+• Recommended dose
+• Seed supply through corporation
+• Early variety (short duration)
+• Grow short-duration variety
+• direct seeding of sprouted seed under puddled condition
+• weed mulching
+• biasi
+• foliar application of urea for established crops
+• Foliar urea if stress
+• Seed supply</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t>• Indira barani dhan-1
 • Danteshwari
-• apply recommended fertilizer [~fuzzy]</t>
+• apply recommended fertilizer [~fuzzy]
+• Recommended dose [~fuzzy]</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2790,30 +3465,33 @@
 • apply 15-20 kg ZnSO4 before planting
 • Recommended dose + 15-20 kg ZnSO4/ha
 • ZnSO4 @15-20 kg/ha
-• ZnSO4 supply</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>20</v>
+• ZnSO4 supply
+• Sawarna
+• Samleshwari
+• Grow short/medium-duration variety
+• direct seeding of sprouted rice seed under puddled condition
+• Seed supply through corporation
+• Early variety (short duration)
+• Grow short-duration variety
+• direct seeding of sprouted seed under puddled condition
+• weed mulching
+• biasi
+• foliar application of urea for established crops
+• Foliar urea if stress
+• Seed supply</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Surajpur · rows 3</t>
+          <t>Surajpur · rows 3, 6, 8</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Normal onset (15 Jun-15 Jul)</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>English response (normal onset)</t>
         </is>
       </c>
     </row>
@@ -2852,28 +3530,75 @@
           <t>Balrampur / upland / No irrigation</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>• Tulsi
+• Vandana
+• Aditya
+• Kalinga-3
+• Samleshwari
+• Vanprabha
+• Indira Barani Dhan-1
+• Anjali
+• Danteshwari
+• Line sowing with recommended dose of fertilizer
+• As recommended
+• Not specified
+• Purnima
+• Annada
+• Direct seeding of sprouted rice seed under puddled condition
+• increase seed rate by 20%
+• Local varieties (no change recommended)
+• Thinning and gap filling of existing crops
+• re-sowing
+• life saving irrigation
+• in situ SWC measures
+• supply of inter-cultural implements
+• farm pond via IWSM</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>• Tulsi
+• Vandana
+• Indira Barani Dhan-1
+• Anjali
+• Danteshwari
+• As recommended [~fuzzy]
+• Purnima
+• Annada [~fuzzy]
+• increase seed rate by 20%
+• Line sowing with recommended dose of fertilizer [~semantic]
+• Direct seeding of sprouted rice seed under puddled condition [~semantic]</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>• Aditya
+• Kalinga-3
+• Samleshwari
+• Vanprabha
+• Not specified
+• Local varieties (no change recommended)
+• Thinning and gap filling of existing crops
+• re-sowing
+• life saving irrigation
+• in situ SWC measures
+• supply of inter-cultural implements
+• farm pond via IWSM</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Balrampur · rows 2, 5, 10</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>No golden dataset match — No row matches (district + land type + irrigation + scenario)</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Normal onset (15 Jun-15 Jul)</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>English response (normal onset)</t>
+          <t>Partial — some key advice missing</t>
         </is>
       </c>
     </row>
@@ -2921,21 +3646,31 @@
 • Danteswari
 • Karma masuri
 • Bambleswari
+• Use 15-20 days old seedling for transplanting
+• apply 15-20 kg ZnSO4 before planting or sowing
+• recommended dose of fertilizer
+• As recommended
+• 15-20 kg ZnSO4/ha
+• Not specified
 • Sowing of sprouted rice seed under lehi condition
 • sowing of medium duration variety
 • proper water management
 • apply 15-20 kg ZnSO4 before planting
 • improved Biasi in direct seeded rice
-• As recommended
-• 15-20 kg ZnSO4/ha
-• Not specified
 • Seed drills under RKVY
-• seed supply through Seed corporation</t>
+• seed supply through Seed corporation
+• Indira sona
+• sowing of medium duration variety with 25% higher seed rate
+• As per normal (no change recommended)
+• Life saving irrigation
+• in situ soil water conservation measures
+• Farm pond through IWSM programme</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>• Bambleswari [~fuzzy]</t>
+          <t>• Bambleswari [~fuzzy]
+• in situ soil water conservation measures [~semantic]</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2948,39 +3683,37 @@
 • Mahamaya
 • Danteswari
 • Karma masuri
+• Use 15-20 days old seedling for transplanting
+• apply 15-20 kg ZnSO4 before planting or sowing
+• recommended dose of fertilizer
+• As recommended
+• 15-20 kg ZnSO4/ha
+• Not specified
 • Sowing of sprouted rice seed under lehi condition
 • sowing of medium duration variety
 • proper water management
 • apply 15-20 kg ZnSO4 before planting
 • improved Biasi in direct seeded rice
-• As recommended
-• 15-20 kg ZnSO4/ha
-• Not specified
 • Seed drills under RKVY
-• seed supply through Seed corporation</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>5.3</v>
+• seed supply through Seed corporation
+• Indira sona
+• sowing of medium duration variety with 25% higher seed rate
+• As per normal (no change recommended)
+• Life saving irrigation
+• Farm pond through IWSM programme</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>7.1</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Jashpur · rows 6</t>
+          <t>Jashpur · rows 3, 6, 8, 12</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Delayed 4 weeks (July 2nd week)</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>English response (4 week delay)</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3753,29 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>• Purnima
+          <t>• Sawarna
+• Jaldubi
+• PA-6444
+• Mahamaya
+• Danteshwari
+• Bambleswari
+• Karma Mahsuri
+• Swarna sub-1
+• Standard transplanting
+• recommended package
+• Recommended dose
+• Normal
+• Sawarna sub-1
+• MTU-1010
+• PHB-71
+• KRH-1
+• Indira sona
+• IGKV R2/Durgeshwari
+• IGKV R1244/Maheshwari
+• Grow short/medium-duration variety
+• direct seeding of sprouted rice seed under puddled condition
+• Seed supply through corporation
+• Purnima
 • MTU-1010 (early + mid-early duration)
 • Short-duration variety
 • sprouted seed under puddled condition
@@ -3033,9 +3788,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>• MTU-1010 (early + mid-early duration) [name match]
+          <t>• Danteshwari [~fuzzy]
+• MTU-1010
+• MTU-1010 (early + mid-early duration) [name match]
 • weed mulching
 • biasi
+• direct seeding of sprouted rice seed under puddled condition [~semantic]
 • sprouted seed under puddled condition [~semantic]
 • foliar urea for established crops [~semantic]
 • Seed supply [~semantic]</t>
@@ -3043,28 +3801,41 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>• Purnima
+          <t>• Sawarna
+• Jaldubi
+• PA-6444
+• Mahamaya
+• Bambleswari
+• Karma Mahsuri
+• Swarna sub-1
+• Standard transplanting
+• recommended package
+• Recommended dose
+• Normal
+• Sawarna sub-1
+• PHB-71
+• KRH-1
+• Indira sona
+• IGKV R2/Durgeshwari
+• IGKV R1244/Maheshwari
+• Grow short/medium-duration variety
+• Seed supply through corporation
+• Purnima
 • Short-duration variety
 • Foliar urea if stress</t>
         </is>
       </c>
-      <c r="H27" s="7" t="n">
-        <v>66.7</v>
+      <c r="H27" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Surajpur · rows 9</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>Delayed 6-8 weeks (1-15 Aug)</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>English response (6 week delay)</t>
+          <t>Surajpur · rows 4, 7, 9</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Low score — review chatbot response</t>
         </is>
       </c>
     </row>
@@ -3105,51 +3876,85 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>• Normal varieties (no change recommended)
+          <t>• Swarna
+• Jaldubi
+• PA-6444
+• Mahamaya
+• Danteshwari
+• Bamleshwari
+• Karma Mahsuri
+• Swarna sub-1
+• IGKV R2
+• IGKV R1244
+• As recommended (standard DACP guidelines)
+• As recommended
+• Not specified
+• MTU-1010
+• PHB-71
+• KRH-1
+• Indira Sona
+• Grow short and medium duration variety
+• direct seeding of sprouted rice seed under puddled condition
+• Purnima
+• Grow short duration variety
+• weed mulching
+• biasi and foliar urea if already sown
+• Foliar application of urea if already sown
+• Normal varieties (no change recommended)
 • Gap filling
 • life saving irrigation
 • in situ SWC measures
+• in situ SWC</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>• weed mulching [~fuzzy]
+• life saving irrigation [~fuzzy]</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>• Swarna
+• Jaldubi
+• PA-6444
+• Mahamaya
+• Danteshwari
+• Bamleshwari
+• Karma Mahsuri
+• Swarna sub-1
+• IGKV R2
+• IGKV R1244
+• As recommended (standard DACP guidelines)
 • As recommended
 • Not specified
-• in situ SWC</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>• life saving irrigation [~fuzzy]</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>• Normal varieties (no change recommended)
+• MTU-1010
+• PHB-71
+• KRH-1
+• Indira Sona
+• Grow short and medium duration variety
+• direct seeding of sprouted rice seed under puddled condition
+• Purnima
+• Grow short duration variety
+• biasi and foliar urea if already sown
+• Foliar application of urea if already sown
+• Normal varieties (no change recommended)
 • Gap filling
 • in situ SWC measures
-• As recommended
-• Not specified
 • in situ SWC</t>
         </is>
       </c>
-      <c r="H28" s="4" t="n">
-        <v>14.3</v>
+      <c r="H28" s="3" t="n">
+        <v>6.9</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Balrampur · rows 12</t>
+          <t>Balrampur · rows 4, 7, 9, 12</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Normal onset followed by 15-20 days dry spell</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>English response (normal onset)</t>
         </is>
       </c>
     </row>
@@ -3189,42 +3994,61 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>• As per normal varieties (no change specified)
+          <t>• Swarna
+• Swarna sub-1
+• Mahamaya
+• Danteswari
+• PA-6444
+• PHB-71
+• KRH-1
+• Indira sona
+• Linseed: R-552
+• Kiran
+• Shital
 • As recommended (standard DACP guidelines)
 • As recommended
-• Not specified</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr"/>
+• Not specified
+• Seed supply through Seed corporation
+• As per normal varieties (no change specified)
+• As per normal (no change recommended)</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>• Swarna
+• Swarna sub-1
+• Mahamaya
+• Danteswari</t>
+        </is>
+      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>• As per normal varieties (no change specified)
+          <t>• PA-6444
+• PHB-71
+• KRH-1
+• Indira sona
+• Linseed: R-552
+• Kiran
+• Shital
 • As recommended (standard DACP guidelines)
 • As recommended
-• Not specified</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>0</v>
+• Not specified
+• Seed supply through Seed corporation
+• As per normal varieties (no change specified)
+• As per normal (no change recommended)</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Jashpur · rows 10</t>
+          <t>Jashpur · rows 4, 7, 9, 10, 13</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Low score — review chatbot response</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Delayed 8 weeks (August 2nd week)</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>English response (8 week delay)</t>
         </is>
       </c>
     </row>
